--- a/output/第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx
+++ b/output/第10期計画_サービス見込量の算定_基準年度とパターンの比較.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総括表は保険者（広域連合）単位、計画作成支援ツールは3町合計です。同じ令和7年度の利用者数でも、3町合計が保険者単位を+1.4％から+243％上回ります。給付費でも令和7年度は3町合計が4.0％上回ります（確認事項No.87）。</t>
+          <t>見える化システムの総括表は保険者（広域連合）単位、計画作成支援ツールは3町合計です。同じ令和7年度の利用者数でも、3町合計が保険者単位を+1.4％から+243％上回ります。給付費は令和6年度から令和8年度まで3町のファイルの合計と広域連合単位のファイルが円単位で一致します（確認事項No.87は解決）。</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>約4.3か月分</t>
+          <t>約4.1か月分</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>約4.3か月分だが値は使える</t>
+          <t>約4.1か月分だが値は使える</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>約4.3か月分だが値は使える</t>
+          <t>約4.1か月分だが値は使える</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -1106,8 +1106,8 @@
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>注1）令和8年度の給付費は令和7年度の36.0％であり、月数に換算するとおおむね4.3か月分に当たります。月数そのものは公表されていないため［要確認］です。
-注2）令和6年度と令和8年度は3町合計と広域連合単位が完全に一致し、令和7年度のみ4.0％の差があります（確認事項No.87）。</t>
+          <t>注1）令和8年度の給付費は令和7年度の34.5％であり、月数に換算するとおおむね4.1か月分に当たります。月数そのものは公表されていないため［要確認］です。
+注2）3町のファイルの合計と広域連合単位のファイルは、令和6年度から令和8年度まで円単位で一致します。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消しました（確認事項No.87）。</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの給付費（広域連合の行）</t>
+          <t>給付費データ集計（広域連合単位のファイル）</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>3,083,474,291</t>
+          <t>3,213,054,558</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -2572,14 +2572,14 @@
       <c r="F41" s="6" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は決算の保険給付費＋介護予防・生活支援サービス事業費とおおむね一致する。年報の給付費とは範囲が異なる</t>
+          <t>「給付費総額」（保険請求額＋保険利用者負担額）の合計であり費用額に当たる。年報の給付費とは範囲が異なる</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの給付費（3町の行の合計）</t>
+          <t>給付費データ集計（3町のファイルの合計）</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -2601,7 +2601,7 @@
       <c r="F42" s="6" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>令和6年度・令和8年度は広域連合の行と完全に一致し、令和7年度のみ129,580,267円（4.2％）上回る（確認事項No.87）</t>
+          <t>令和6年度から令和8年度まで広域連合単位のファイルと完全に一致する。令和7年度にあった129,580,267円の差は、令和8年9月25日に再提供を受けたファイルにより解消した（確認事項No.87）</t>
         </is>
       </c>
     </row>
@@ -2659,14 +2659,14 @@
       <c r="F44" s="6" t="inlineStr"/>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの給付費合計との差は-5,775円</t>
+          <t>給付費データ集計の合計との差は-5,775円</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>注）計画作成支援ツールの給付費合計は、令和6年度において決算の保険給付費（款2）に介護予防・生活支援サービス事業費を加えた額と5,775円の差で一致します。ツールの給付費は総合事業費を含む範囲であるとみられます。［要確認］</t>
+          <t>注）給付費データ集計の給付費（給付費総額）の合計は、令和6年度において決算の保険給付費（款2）に介護予防・生活支援サービス事業費を加えた額と5,775円の差で一致します。給付費データの給付費総額は総合事業費を含む範囲であるとみられます。［要確認］</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>3町合計は町をまたぐ計上の重複を含み、令和7年度の給付費で広域連合単位を4.0％上回る（確認事項No.87）。保険料は保険者単位で算定するため、算定の基礎には用いられない。町別の実績を掲げる用途には用いる。</t>
+          <t>3町合計は利用者数において広域連合単位を大きく上回る（区域外の施設を利用する被保険者と区域内の施設を利用する他保険者の被保険者の扱いが違う）。保険料は保険者単位で算定するため、算定の基礎には用いられない。町別の実績を掲げる用途には用いる。</t>
         </is>
       </c>
     </row>
@@ -5425,17 +5425,17 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>3町合計と広域連合単位の給付費の差が令和7年度のみに生じること</t>
+          <t>3町合計と広域連合単位の給付費がいずれの年度も一致すること</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>R6 0円／R7 129,580,267円／R8 0円</t>
+          <t>R6 0円／R7 0円／R8 0円</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>令和6年度・令和8年度は一致、令和7年度のみ4.2％の差</t>
+          <t>3か年とも円単位で一致（令和7年度の差は再提供により解消した）</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>3町合計と広域連合単位の給付費の差（令和7年度4.0％）</t>
+          <t>給付費データの給付費総額と年報の給付費の範囲の違い</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.87として照会中である。本表では広域連合単位を用いている</t>
+          <t>給付費総額は保険請求額＋保険利用者負担額であり費用額に当たる。本表の算定は年報及び総括表（保険給付費）によっている</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>給付費が令和7年度の36.0％であることから、おおむね4.3か月分と見ているが、月数そのものは公表されていない。令和8年度を実績として掲げる場合、月数の明記が要る。</t>
+          <t>給付費が令和7年度の34.5％であることから、おおむね4.1か月分と見ているが、月数そのものは公表されていない。令和8年度を実績として掲げる場合、月数の明記が要る。</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
